--- a/templates/oefen/oefen_bodem_template_full.xlsx
+++ b/templates/oefen/oefen_bodem_template_full.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16324" uniqueCount="2882">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16328" uniqueCount="2884">
   <si>
     <t>metadata-type</t>
   </si>
@@ -8018,6 +8018,12 @@
     <t>https://data.bodemenondergrond.vlaanderen.be/id/concept/bemonsteringsprocedure/bam</t>
   </si>
   <si>
+    <t>https://data.bodemenondergrond.vlaanderen.be/id/concept/bemonsteringsprocedure/bbb</t>
+  </si>
+  <si>
+    <t>https://data.bodemenondergrond.vlaanderen.be/id/concept/bemonsteringsprocedure/bbo</t>
+  </si>
+  <si>
     <t>https://data.bodemenondergrond.vlaanderen.be/id/concept/bemonsteringsprocedure/boc</t>
   </si>
   <si>
@@ -8639,13 +8645,13 @@
     <t>Date generated</t>
   </si>
   <si>
-    <t>2026-03-31 16:51:48.877940</t>
+    <t>2026-05-06 16:21:32.226048</t>
   </si>
   <si>
     <t>version</t>
   </si>
   <si>
-    <t>2.3.0</t>
+    <t>2.3.1</t>
   </si>
   <si>
     <t>xdov-version</t>
@@ -9542,7 +9548,7 @@
 </file>
 
 <file path=xl/tables/table76.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="76" name="Table76" displayName="Table76" ref="EU3:EV12" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="76" name="Table76" displayName="Table76" ref="EU3:EV14" totalsRowShown="0">
   <tableColumns count="2">
     <tableColumn id="1" name="Code"/>
     <tableColumn id="2" name="Beschrijving"/>
@@ -10250,7 +10256,7 @@
       <c r="EM1" s="1"/>
       <c r="EN1" s="1"/>
       <c r="EO1" s="1" t="s">
-        <v>2709</v>
+        <v>2711</v>
       </c>
       <c r="EP1" s="1"/>
       <c r="EQ1" s="1"/>
@@ -10266,7 +10272,7 @@
       <c r="FA1" s="1"/>
       <c r="FB1" s="1"/>
       <c r="FC1" s="1" t="s">
-        <v>2736</v>
+        <v>2738</v>
       </c>
       <c r="FD1" s="1"/>
       <c r="FE1" s="1"/>
@@ -10630,15 +10636,15 @@
       </c>
       <c r="FB2" s="1"/>
       <c r="FC2" s="1" t="s">
-        <v>2710</v>
+        <v>2712</v>
       </c>
       <c r="FD2" s="1"/>
       <c r="FE2" s="1" t="s">
-        <v>2725</v>
+        <v>2727</v>
       </c>
       <c r="FF2" s="1"/>
       <c r="FG2" s="1" t="s">
-        <v>2726</v>
+        <v>2728</v>
       </c>
       <c r="FH2" s="1"/>
       <c r="FI2" s="1" t="s">
@@ -10702,11 +10708,11 @@
       </c>
       <c r="GL2" s="1"/>
       <c r="GM2" s="1" t="s">
-        <v>2825</v>
+        <v>2827</v>
       </c>
       <c r="GN2" s="1"/>
       <c r="GO2" s="1" t="s">
-        <v>2827</v>
+        <v>2829</v>
       </c>
       <c r="GP2" s="1"/>
       <c r="GQ2" s="1" t="s">
@@ -11774,13 +11780,13 @@
         <v>81</v>
       </c>
       <c r="EW4" s="2" t="s">
-        <v>2669</v>
+        <v>2671</v>
       </c>
       <c r="EX4" t="s">
         <v>81</v>
       </c>
       <c r="EY4" s="2" t="s">
-        <v>2706</v>
+        <v>2708</v>
       </c>
       <c r="EZ4" t="s">
         <v>81</v>
@@ -11834,7 +11840,7 @@
         <v>81</v>
       </c>
       <c r="FQ4" s="2" t="s">
-        <v>2733</v>
+        <v>2735</v>
       </c>
       <c r="FR4" t="s">
         <v>81</v>
@@ -11900,13 +11906,13 @@
         <v>81</v>
       </c>
       <c r="GM4" t="s">
-        <v>2830</v>
+        <v>2832</v>
       </c>
       <c r="GN4" t="s">
         <v>81</v>
       </c>
       <c r="GO4" t="s">
-        <v>2844</v>
+        <v>2846</v>
       </c>
       <c r="GP4" t="s">
         <v>81</v>
@@ -12376,13 +12382,13 @@
         <v>81</v>
       </c>
       <c r="EW5" s="2" t="s">
-        <v>2670</v>
+        <v>2672</v>
       </c>
       <c r="EX5" t="s">
         <v>81</v>
       </c>
       <c r="EY5" s="2" t="s">
-        <v>2707</v>
+        <v>2709</v>
       </c>
       <c r="EZ5" t="s">
         <v>81</v>
@@ -12436,7 +12442,7 @@
         <v>81</v>
       </c>
       <c r="FQ5" s="2" t="s">
-        <v>2734</v>
+        <v>2736</v>
       </c>
       <c r="FR5" t="s">
         <v>81</v>
@@ -12502,13 +12508,13 @@
         <v>81</v>
       </c>
       <c r="GM5" t="s">
-        <v>2831</v>
+        <v>2833</v>
       </c>
       <c r="GN5" t="s">
         <v>81</v>
       </c>
       <c r="GO5" t="s">
-        <v>2845</v>
+        <v>2847</v>
       </c>
       <c r="GP5" t="s">
         <v>81</v>
@@ -12936,13 +12942,13 @@
         <v>81</v>
       </c>
       <c r="EW6" s="2" t="s">
-        <v>2671</v>
+        <v>2673</v>
       </c>
       <c r="EX6" t="s">
         <v>81</v>
       </c>
       <c r="EY6" s="2" t="s">
-        <v>2708</v>
+        <v>2710</v>
       </c>
       <c r="EZ6" t="s">
         <v>81</v>
@@ -12996,7 +13002,7 @@
         <v>81</v>
       </c>
       <c r="FQ6" s="2" t="s">
-        <v>2735</v>
+        <v>2737</v>
       </c>
       <c r="FR6" t="s">
         <v>81</v>
@@ -13056,13 +13062,13 @@
         <v>81</v>
       </c>
       <c r="GM6" t="s">
-        <v>2832</v>
+        <v>2834</v>
       </c>
       <c r="GN6" t="s">
         <v>81</v>
       </c>
       <c r="GO6" t="s">
-        <v>2846</v>
+        <v>2848</v>
       </c>
       <c r="GP6" t="s">
         <v>81</v>
@@ -13376,7 +13382,7 @@
         <v>81</v>
       </c>
       <c r="EW7" s="2" t="s">
-        <v>2672</v>
+        <v>2674</v>
       </c>
       <c r="EX7" t="s">
         <v>81</v>
@@ -13460,13 +13466,13 @@
         <v>81</v>
       </c>
       <c r="GM7" t="s">
-        <v>2833</v>
+        <v>2835</v>
       </c>
       <c r="GN7" t="s">
         <v>81</v>
       </c>
       <c r="GO7" t="s">
-        <v>2847</v>
+        <v>2849</v>
       </c>
       <c r="GP7" t="s">
         <v>81</v>
@@ -13762,7 +13768,7 @@
         <v>81</v>
       </c>
       <c r="EW8" s="2" t="s">
-        <v>2673</v>
+        <v>2675</v>
       </c>
       <c r="EX8" t="s">
         <v>81</v>
@@ -13846,13 +13852,13 @@
         <v>81</v>
       </c>
       <c r="GM8" t="s">
-        <v>2834</v>
+        <v>2836</v>
       </c>
       <c r="GN8" t="s">
         <v>81</v>
       </c>
       <c r="GO8" t="s">
-        <v>2848</v>
+        <v>2850</v>
       </c>
       <c r="GP8" t="s">
         <v>81</v>
@@ -14118,7 +14124,7 @@
         <v>81</v>
       </c>
       <c r="EW9" s="2" t="s">
-        <v>2674</v>
+        <v>2676</v>
       </c>
       <c r="EX9" t="s">
         <v>81</v>
@@ -14196,13 +14202,13 @@
         <v>81</v>
       </c>
       <c r="GM9" t="s">
-        <v>2835</v>
+        <v>2837</v>
       </c>
       <c r="GN9" t="s">
         <v>81</v>
       </c>
       <c r="GO9" t="s">
-        <v>2849</v>
+        <v>2851</v>
       </c>
       <c r="GP9" t="s">
         <v>81</v>
@@ -14444,7 +14450,7 @@
         <v>81</v>
       </c>
       <c r="EW10" s="2" t="s">
-        <v>2675</v>
+        <v>2677</v>
       </c>
       <c r="EX10" t="s">
         <v>81</v>
@@ -14516,13 +14522,13 @@
         <v>81</v>
       </c>
       <c r="GM10" t="s">
-        <v>2836</v>
+        <v>2838</v>
       </c>
       <c r="GN10" t="s">
         <v>81</v>
       </c>
       <c r="GO10" t="s">
-        <v>2850</v>
+        <v>2852</v>
       </c>
       <c r="GP10" t="s">
         <v>81</v>
@@ -14764,7 +14770,7 @@
         <v>81</v>
       </c>
       <c r="EW11" s="2" t="s">
-        <v>2676</v>
+        <v>2678</v>
       </c>
       <c r="EX11" t="s">
         <v>81</v>
@@ -14836,13 +14842,13 @@
         <v>81</v>
       </c>
       <c r="GM11" t="s">
-        <v>2837</v>
+        <v>2839</v>
       </c>
       <c r="GN11" t="s">
         <v>81</v>
       </c>
       <c r="GO11" t="s">
-        <v>2851</v>
+        <v>2853</v>
       </c>
       <c r="GP11" t="s">
         <v>81</v>
@@ -15084,7 +15090,7 @@
         <v>81</v>
       </c>
       <c r="EW12" s="2" t="s">
-        <v>2677</v>
+        <v>2679</v>
       </c>
       <c r="EX12" t="s">
         <v>81</v>
@@ -15156,13 +15162,13 @@
         <v>81</v>
       </c>
       <c r="GM12" t="s">
-        <v>2838</v>
+        <v>2840</v>
       </c>
       <c r="GN12" t="s">
         <v>81</v>
       </c>
       <c r="GO12" t="s">
-        <v>2852</v>
+        <v>2854</v>
       </c>
       <c r="GP12" t="s">
         <v>81</v>
@@ -15397,8 +15403,14 @@
       <c r="ET13" t="s">
         <v>81</v>
       </c>
+      <c r="EU13" s="2" t="s">
+        <v>2669</v>
+      </c>
+      <c r="EV13" t="s">
+        <v>81</v>
+      </c>
       <c r="EW13" s="2" t="s">
-        <v>2678</v>
+        <v>2680</v>
       </c>
       <c r="EX13" t="s">
         <v>81</v>
@@ -15470,13 +15482,13 @@
         <v>81</v>
       </c>
       <c r="GM13" t="s">
-        <v>2839</v>
+        <v>2841</v>
       </c>
       <c r="GN13" t="s">
         <v>81</v>
       </c>
       <c r="GO13" t="s">
-        <v>2853</v>
+        <v>2855</v>
       </c>
       <c r="GP13" t="s">
         <v>81</v>
@@ -15705,8 +15717,14 @@
       <c r="ET14" t="s">
         <v>81</v>
       </c>
+      <c r="EU14" s="2" t="s">
+        <v>2670</v>
+      </c>
+      <c r="EV14" t="s">
+        <v>81</v>
+      </c>
       <c r="EW14" s="2" t="s">
-        <v>2679</v>
+        <v>2681</v>
       </c>
       <c r="EX14" t="s">
         <v>81</v>
@@ -15778,13 +15796,13 @@
         <v>81</v>
       </c>
       <c r="GM14" t="s">
-        <v>2840</v>
+        <v>2842</v>
       </c>
       <c r="GN14" t="s">
         <v>81</v>
       </c>
       <c r="GO14" t="s">
-        <v>2854</v>
+        <v>2856</v>
       </c>
       <c r="GP14" t="s">
         <v>81</v>
@@ -16008,7 +16026,7 @@
         <v>81</v>
       </c>
       <c r="EW15" s="2" t="s">
-        <v>2680</v>
+        <v>2682</v>
       </c>
       <c r="EX15" t="s">
         <v>81</v>
@@ -16080,13 +16098,13 @@
         <v>81</v>
       </c>
       <c r="GM15" t="s">
-        <v>2841</v>
+        <v>2843</v>
       </c>
       <c r="GN15" t="s">
         <v>81</v>
       </c>
       <c r="GO15" t="s">
-        <v>2855</v>
+        <v>2857</v>
       </c>
       <c r="GP15" t="s">
         <v>81</v>
@@ -16304,7 +16322,7 @@
         <v>81</v>
       </c>
       <c r="EW16" s="2" t="s">
-        <v>2681</v>
+        <v>2683</v>
       </c>
       <c r="EX16" t="s">
         <v>81</v>
@@ -16376,13 +16394,13 @@
         <v>81</v>
       </c>
       <c r="GM16" t="s">
-        <v>2842</v>
+        <v>2844</v>
       </c>
       <c r="GN16" t="s">
         <v>81</v>
       </c>
       <c r="GO16" t="s">
-        <v>2856</v>
+        <v>2858</v>
       </c>
       <c r="GP16" t="s">
         <v>81</v>
@@ -16600,7 +16618,7 @@
         <v>81</v>
       </c>
       <c r="EW17" s="2" t="s">
-        <v>2682</v>
+        <v>2684</v>
       </c>
       <c r="EX17" t="s">
         <v>81</v>
@@ -16678,7 +16696,7 @@
         <v>81</v>
       </c>
       <c r="GO17" t="s">
-        <v>2857</v>
+        <v>2859</v>
       </c>
       <c r="GP17" t="s">
         <v>81</v>
@@ -16866,7 +16884,7 @@
         <v>81</v>
       </c>
       <c r="EW18" s="2" t="s">
-        <v>2683</v>
+        <v>2685</v>
       </c>
       <c r="EX18" t="s">
         <v>81</v>
@@ -16932,13 +16950,13 @@
         <v>81</v>
       </c>
       <c r="GM18" t="s">
-        <v>2843</v>
+        <v>2845</v>
       </c>
       <c r="GN18" t="s">
         <v>81</v>
       </c>
       <c r="GO18" t="s">
-        <v>2858</v>
+        <v>2860</v>
       </c>
       <c r="GP18" t="s">
         <v>81</v>
@@ -17120,7 +17138,7 @@
         <v>81</v>
       </c>
       <c r="EW19" s="2" t="s">
-        <v>2684</v>
+        <v>2686</v>
       </c>
       <c r="EX19" t="s">
         <v>81</v>
@@ -17186,7 +17204,7 @@
         <v>81</v>
       </c>
       <c r="GO19" t="s">
-        <v>2859</v>
+        <v>2861</v>
       </c>
       <c r="GP19" t="s">
         <v>81</v>
@@ -17362,7 +17380,7 @@
         <v>81</v>
       </c>
       <c r="EW20" s="2" t="s">
-        <v>2685</v>
+        <v>2687</v>
       </c>
       <c r="EX20" t="s">
         <v>81</v>
@@ -17428,7 +17446,7 @@
         <v>81</v>
       </c>
       <c r="GO20" t="s">
-        <v>2860</v>
+        <v>2862</v>
       </c>
       <c r="GP20" t="s">
         <v>81</v>
@@ -17574,7 +17592,7 @@
         <v>81</v>
       </c>
       <c r="EW21" s="2" t="s">
-        <v>2686</v>
+        <v>2688</v>
       </c>
       <c r="EX21" t="s">
         <v>81</v>
@@ -17634,7 +17652,7 @@
         <v>81</v>
       </c>
       <c r="GO21" t="s">
-        <v>2861</v>
+        <v>2863</v>
       </c>
       <c r="GP21" t="s">
         <v>81</v>
@@ -17768,7 +17786,7 @@
         <v>81</v>
       </c>
       <c r="EW22" s="2" t="s">
-        <v>2687</v>
+        <v>2689</v>
       </c>
       <c r="EX22" t="s">
         <v>81</v>
@@ -17828,7 +17846,7 @@
         <v>81</v>
       </c>
       <c r="GO22" t="s">
-        <v>2862</v>
+        <v>2864</v>
       </c>
       <c r="GP22" t="s">
         <v>81</v>
@@ -17962,7 +17980,7 @@
         <v>81</v>
       </c>
       <c r="EW23" s="2" t="s">
-        <v>2688</v>
+        <v>2690</v>
       </c>
       <c r="EX23" t="s">
         <v>81</v>
@@ -18022,7 +18040,7 @@
         <v>81</v>
       </c>
       <c r="GO23" t="s">
-        <v>2863</v>
+        <v>2865</v>
       </c>
       <c r="GP23" t="s">
         <v>81</v>
@@ -18144,7 +18162,7 @@
         <v>81</v>
       </c>
       <c r="EW24" s="2" t="s">
-        <v>2689</v>
+        <v>2691</v>
       </c>
       <c r="EX24" t="s">
         <v>81</v>
@@ -18204,7 +18222,7 @@
         <v>81</v>
       </c>
       <c r="GO24" t="s">
-        <v>2864</v>
+        <v>2866</v>
       </c>
       <c r="GP24" t="s">
         <v>81</v>
@@ -18320,7 +18338,7 @@
         <v>81</v>
       </c>
       <c r="EW25" s="2" t="s">
-        <v>2690</v>
+        <v>2692</v>
       </c>
       <c r="EX25" t="s">
         <v>81</v>
@@ -18380,7 +18398,7 @@
         <v>81</v>
       </c>
       <c r="GO25" t="s">
-        <v>2865</v>
+        <v>2867</v>
       </c>
       <c r="GP25" t="s">
         <v>81</v>
@@ -18496,7 +18514,7 @@
         <v>81</v>
       </c>
       <c r="EW26" s="2" t="s">
-        <v>2691</v>
+        <v>2693</v>
       </c>
       <c r="EX26" t="s">
         <v>81</v>
@@ -18556,7 +18574,7 @@
         <v>81</v>
       </c>
       <c r="GO26" t="s">
-        <v>2866</v>
+        <v>2868</v>
       </c>
       <c r="GP26" t="s">
         <v>81</v>
@@ -18672,7 +18690,7 @@
         <v>81</v>
       </c>
       <c r="EW27" s="2" t="s">
-        <v>2692</v>
+        <v>2694</v>
       </c>
       <c r="EX27" t="s">
         <v>81</v>
@@ -18732,7 +18750,7 @@
         <v>81</v>
       </c>
       <c r="GO27" t="s">
-        <v>2867</v>
+        <v>2869</v>
       </c>
       <c r="GP27" t="s">
         <v>81</v>
@@ -18848,7 +18866,7 @@
         <v>81</v>
       </c>
       <c r="EW28" s="2" t="s">
-        <v>2693</v>
+        <v>2695</v>
       </c>
       <c r="EX28" t="s">
         <v>81</v>
@@ -18908,7 +18926,7 @@
         <v>81</v>
       </c>
       <c r="GO28" t="s">
-        <v>2868</v>
+        <v>2870</v>
       </c>
       <c r="GP28" t="s">
         <v>81</v>
@@ -19024,7 +19042,7 @@
         <v>81</v>
       </c>
       <c r="EW29" s="2" t="s">
-        <v>2694</v>
+        <v>2696</v>
       </c>
       <c r="EX29" t="s">
         <v>81</v>
@@ -19084,7 +19102,7 @@
         <v>81</v>
       </c>
       <c r="GO29" t="s">
-        <v>2869</v>
+        <v>2871</v>
       </c>
       <c r="GP29" t="s">
         <v>81</v>
@@ -19200,7 +19218,7 @@
         <v>81</v>
       </c>
       <c r="EW30" s="2" t="s">
-        <v>2695</v>
+        <v>2697</v>
       </c>
       <c r="EX30" t="s">
         <v>81</v>
@@ -19370,7 +19388,7 @@
         <v>81</v>
       </c>
       <c r="EW31" s="2" t="s">
-        <v>2696</v>
+        <v>2698</v>
       </c>
       <c r="EX31" t="s">
         <v>81</v>
@@ -19540,7 +19558,7 @@
         <v>81</v>
       </c>
       <c r="EW32" s="2" t="s">
-        <v>2697</v>
+        <v>2699</v>
       </c>
       <c r="EX32" t="s">
         <v>81</v>
@@ -19710,7 +19728,7 @@
         <v>81</v>
       </c>
       <c r="EW33" s="2" t="s">
-        <v>2698</v>
+        <v>2700</v>
       </c>
       <c r="EX33" t="s">
         <v>81</v>
@@ -19880,7 +19898,7 @@
         <v>81</v>
       </c>
       <c r="EW34" s="2" t="s">
-        <v>2699</v>
+        <v>2701</v>
       </c>
       <c r="EX34" t="s">
         <v>81</v>
@@ -20050,7 +20068,7 @@
         <v>81</v>
       </c>
       <c r="EW35" s="2" t="s">
-        <v>2700</v>
+        <v>2702</v>
       </c>
       <c r="EX35" t="s">
         <v>81</v>
@@ -20220,7 +20238,7 @@
         <v>81</v>
       </c>
       <c r="EW36" s="2" t="s">
-        <v>2701</v>
+        <v>2703</v>
       </c>
       <c r="EX36" t="s">
         <v>81</v>
@@ -20384,7 +20402,7 @@
         <v>81</v>
       </c>
       <c r="EW37" s="2" t="s">
-        <v>2702</v>
+        <v>2704</v>
       </c>
       <c r="EX37" t="s">
         <v>81</v>
@@ -20548,7 +20566,7 @@
         <v>81</v>
       </c>
       <c r="EW38" s="2" t="s">
-        <v>2703</v>
+        <v>2705</v>
       </c>
       <c r="EX38" t="s">
         <v>81</v>
@@ -20712,7 +20730,7 @@
         <v>81</v>
       </c>
       <c r="EW39" s="2" t="s">
-        <v>2704</v>
+        <v>2706</v>
       </c>
       <c r="EX39" t="s">
         <v>81</v>
@@ -20876,7 +20894,7 @@
         <v>81</v>
       </c>
       <c r="EW40" s="2" t="s">
-        <v>2705</v>
+        <v>2707</v>
       </c>
       <c r="EX40" t="s">
         <v>81</v>
@@ -52735,113 +52753,113 @@
     <hyperlink ref="EU12" r:id="rId32"/>
     <hyperlink ref="EW12" r:id="rId33"/>
     <hyperlink ref="ES13" r:id="rId34"/>
-    <hyperlink ref="EW13" r:id="rId35"/>
-    <hyperlink ref="ES14" r:id="rId36"/>
-    <hyperlink ref="EW14" r:id="rId37"/>
-    <hyperlink ref="ES15" r:id="rId38"/>
-    <hyperlink ref="EW15" r:id="rId39"/>
-    <hyperlink ref="ES16" r:id="rId40"/>
-    <hyperlink ref="EW16" r:id="rId41"/>
-    <hyperlink ref="ES17" r:id="rId42"/>
-    <hyperlink ref="EW17" r:id="rId43"/>
-    <hyperlink ref="ES18" r:id="rId44"/>
-    <hyperlink ref="EW18" r:id="rId45"/>
-    <hyperlink ref="ES19" r:id="rId46"/>
-    <hyperlink ref="EW19" r:id="rId47"/>
-    <hyperlink ref="ES20" r:id="rId48"/>
-    <hyperlink ref="EW20" r:id="rId49"/>
-    <hyperlink ref="ES21" r:id="rId50"/>
-    <hyperlink ref="EW21" r:id="rId51"/>
-    <hyperlink ref="ES22" r:id="rId52"/>
-    <hyperlink ref="EW22" r:id="rId53"/>
-    <hyperlink ref="ES23" r:id="rId54"/>
-    <hyperlink ref="EW23" r:id="rId55"/>
-    <hyperlink ref="ES24" r:id="rId56"/>
-    <hyperlink ref="EW24" r:id="rId57"/>
-    <hyperlink ref="ES25" r:id="rId58"/>
-    <hyperlink ref="EW25" r:id="rId59"/>
-    <hyperlink ref="ES26" r:id="rId60"/>
-    <hyperlink ref="EW26" r:id="rId61"/>
-    <hyperlink ref="ES27" r:id="rId62"/>
-    <hyperlink ref="EW27" r:id="rId63"/>
-    <hyperlink ref="ES28" r:id="rId64"/>
-    <hyperlink ref="EW28" r:id="rId65"/>
-    <hyperlink ref="ES29" r:id="rId66"/>
-    <hyperlink ref="EW29" r:id="rId67"/>
-    <hyperlink ref="ES30" r:id="rId68"/>
-    <hyperlink ref="EW30" r:id="rId69"/>
-    <hyperlink ref="ES31" r:id="rId70"/>
-    <hyperlink ref="EW31" r:id="rId71"/>
-    <hyperlink ref="ES32" r:id="rId72"/>
-    <hyperlink ref="EW32" r:id="rId73"/>
-    <hyperlink ref="ES33" r:id="rId74"/>
-    <hyperlink ref="EW33" r:id="rId75"/>
-    <hyperlink ref="ES34" r:id="rId76"/>
-    <hyperlink ref="EW34" r:id="rId77"/>
-    <hyperlink ref="ES35" r:id="rId78"/>
-    <hyperlink ref="EW35" r:id="rId79"/>
-    <hyperlink ref="ES36" r:id="rId80"/>
-    <hyperlink ref="EW36" r:id="rId81"/>
-    <hyperlink ref="ES37" r:id="rId82"/>
-    <hyperlink ref="EW37" r:id="rId83"/>
-    <hyperlink ref="ES38" r:id="rId84"/>
-    <hyperlink ref="EW38" r:id="rId85"/>
-    <hyperlink ref="ES39" r:id="rId86"/>
-    <hyperlink ref="EW39" r:id="rId87"/>
-    <hyperlink ref="ES40" r:id="rId88"/>
-    <hyperlink ref="EW40" r:id="rId89"/>
-    <hyperlink ref="ES41" r:id="rId90"/>
-    <hyperlink ref="ES42" r:id="rId91"/>
-    <hyperlink ref="ES43" r:id="rId92"/>
-    <hyperlink ref="ES44" r:id="rId93"/>
-    <hyperlink ref="ES45" r:id="rId94"/>
-    <hyperlink ref="ES46" r:id="rId95"/>
-    <hyperlink ref="ES47" r:id="rId96"/>
-    <hyperlink ref="ES48" r:id="rId97"/>
-    <hyperlink ref="ES49" r:id="rId98"/>
-    <hyperlink ref="ES50" r:id="rId99"/>
-    <hyperlink ref="ES51" r:id="rId100"/>
-    <hyperlink ref="ES52" r:id="rId101"/>
-    <hyperlink ref="ES53" r:id="rId102"/>
-    <hyperlink ref="ES54" r:id="rId103"/>
-    <hyperlink ref="ES55" r:id="rId104"/>
-    <hyperlink ref="ES56" r:id="rId105"/>
-    <hyperlink ref="ES57" r:id="rId106"/>
-    <hyperlink ref="ES58" r:id="rId107"/>
-    <hyperlink ref="ES59" r:id="rId108"/>
-    <hyperlink ref="ES60" r:id="rId109"/>
-    <hyperlink ref="ES61" r:id="rId110"/>
-    <hyperlink ref="ES62" r:id="rId111"/>
-    <hyperlink ref="ES63" r:id="rId112"/>
-    <hyperlink ref="ES64" r:id="rId113"/>
-    <hyperlink ref="ES65" r:id="rId114"/>
-    <hyperlink ref="ES66" r:id="rId115"/>
-    <hyperlink ref="ES67" r:id="rId116"/>
-    <hyperlink ref="ES68" r:id="rId117"/>
-    <hyperlink ref="ES69" r:id="rId118"/>
-    <hyperlink ref="ES70" r:id="rId119"/>
-    <hyperlink ref="ES71" r:id="rId120"/>
-    <hyperlink ref="ES72" r:id="rId121"/>
-    <hyperlink ref="ES73" r:id="rId122"/>
-    <hyperlink ref="ES74" r:id="rId123"/>
-    <hyperlink ref="ES75" r:id="rId124"/>
-    <hyperlink ref="ES76" r:id="rId125"/>
-    <hyperlink ref="ES77" r:id="rId126"/>
-    <hyperlink ref="ES78" r:id="rId127"/>
-    <hyperlink ref="ES79" r:id="rId128"/>
-    <hyperlink ref="ES80" r:id="rId129"/>
-    <hyperlink ref="ES81" r:id="rId130"/>
-    <hyperlink ref="ES82" r:id="rId131"/>
-    <hyperlink ref="ES83" r:id="rId132"/>
-    <hyperlink ref="ES84" r:id="rId133"/>
-    <hyperlink ref="ES85" r:id="rId134"/>
-    <hyperlink ref="ES86" r:id="rId135"/>
-    <hyperlink ref="ES87" r:id="rId136"/>
+    <hyperlink ref="EU13" r:id="rId35"/>
+    <hyperlink ref="EW13" r:id="rId36"/>
+    <hyperlink ref="ES14" r:id="rId37"/>
+    <hyperlink ref="EU14" r:id="rId38"/>
+    <hyperlink ref="EW14" r:id="rId39"/>
+    <hyperlink ref="ES15" r:id="rId40"/>
+    <hyperlink ref="EW15" r:id="rId41"/>
+    <hyperlink ref="ES16" r:id="rId42"/>
+    <hyperlink ref="EW16" r:id="rId43"/>
+    <hyperlink ref="ES17" r:id="rId44"/>
+    <hyperlink ref="EW17" r:id="rId45"/>
+    <hyperlink ref="ES18" r:id="rId46"/>
+    <hyperlink ref="EW18" r:id="rId47"/>
+    <hyperlink ref="ES19" r:id="rId48"/>
+    <hyperlink ref="EW19" r:id="rId49"/>
+    <hyperlink ref="ES20" r:id="rId50"/>
+    <hyperlink ref="EW20" r:id="rId51"/>
+    <hyperlink ref="ES21" r:id="rId52"/>
+    <hyperlink ref="EW21" r:id="rId53"/>
+    <hyperlink ref="ES22" r:id="rId54"/>
+    <hyperlink ref="EW22" r:id="rId55"/>
+    <hyperlink ref="ES23" r:id="rId56"/>
+    <hyperlink ref="EW23" r:id="rId57"/>
+    <hyperlink ref="ES24" r:id="rId58"/>
+    <hyperlink ref="EW24" r:id="rId59"/>
+    <hyperlink ref="ES25" r:id="rId60"/>
+    <hyperlink ref="EW25" r:id="rId61"/>
+    <hyperlink ref="ES26" r:id="rId62"/>
+    <hyperlink ref="EW26" r:id="rId63"/>
+    <hyperlink ref="ES27" r:id="rId64"/>
+    <hyperlink ref="EW27" r:id="rId65"/>
+    <hyperlink ref="ES28" r:id="rId66"/>
+    <hyperlink ref="EW28" r:id="rId67"/>
+    <hyperlink ref="ES29" r:id="rId68"/>
+    <hyperlink ref="EW29" r:id="rId69"/>
+    <hyperlink ref="ES30" r:id="rId70"/>
+    <hyperlink ref="EW30" r:id="rId71"/>
+    <hyperlink ref="ES31" r:id="rId72"/>
+    <hyperlink ref="EW31" r:id="rId73"/>
+    <hyperlink ref="ES32" r:id="rId74"/>
+    <hyperlink ref="EW32" r:id="rId75"/>
+    <hyperlink ref="ES33" r:id="rId76"/>
+    <hyperlink ref="EW33" r:id="rId77"/>
+    <hyperlink ref="ES34" r:id="rId78"/>
+    <hyperlink ref="EW34" r:id="rId79"/>
+    <hyperlink ref="ES35" r:id="rId80"/>
+    <hyperlink ref="EW35" r:id="rId81"/>
+    <hyperlink ref="ES36" r:id="rId82"/>
+    <hyperlink ref="EW36" r:id="rId83"/>
+    <hyperlink ref="ES37" r:id="rId84"/>
+    <hyperlink ref="EW37" r:id="rId85"/>
+    <hyperlink ref="ES38" r:id="rId86"/>
+    <hyperlink ref="EW38" r:id="rId87"/>
+    <hyperlink ref="ES39" r:id="rId88"/>
+    <hyperlink ref="EW39" r:id="rId89"/>
+    <hyperlink ref="ES40" r:id="rId90"/>
+    <hyperlink ref="EW40" r:id="rId91"/>
+    <hyperlink ref="ES41" r:id="rId92"/>
+    <hyperlink ref="ES42" r:id="rId93"/>
+    <hyperlink ref="ES43" r:id="rId94"/>
+    <hyperlink ref="ES44" r:id="rId95"/>
+    <hyperlink ref="ES45" r:id="rId96"/>
+    <hyperlink ref="ES46" r:id="rId97"/>
+    <hyperlink ref="ES47" r:id="rId98"/>
+    <hyperlink ref="ES48" r:id="rId99"/>
+    <hyperlink ref="ES49" r:id="rId100"/>
+    <hyperlink ref="ES50" r:id="rId101"/>
+    <hyperlink ref="ES51" r:id="rId102"/>
+    <hyperlink ref="ES52" r:id="rId103"/>
+    <hyperlink ref="ES53" r:id="rId104"/>
+    <hyperlink ref="ES54" r:id="rId105"/>
+    <hyperlink ref="ES55" r:id="rId106"/>
+    <hyperlink ref="ES56" r:id="rId107"/>
+    <hyperlink ref="ES57" r:id="rId108"/>
+    <hyperlink ref="ES58" r:id="rId109"/>
+    <hyperlink ref="ES59" r:id="rId110"/>
+    <hyperlink ref="ES60" r:id="rId111"/>
+    <hyperlink ref="ES61" r:id="rId112"/>
+    <hyperlink ref="ES62" r:id="rId113"/>
+    <hyperlink ref="ES63" r:id="rId114"/>
+    <hyperlink ref="ES64" r:id="rId115"/>
+    <hyperlink ref="ES65" r:id="rId116"/>
+    <hyperlink ref="ES66" r:id="rId117"/>
+    <hyperlink ref="ES67" r:id="rId118"/>
+    <hyperlink ref="ES68" r:id="rId119"/>
+    <hyperlink ref="ES69" r:id="rId120"/>
+    <hyperlink ref="ES70" r:id="rId121"/>
+    <hyperlink ref="ES71" r:id="rId122"/>
+    <hyperlink ref="ES72" r:id="rId123"/>
+    <hyperlink ref="ES73" r:id="rId124"/>
+    <hyperlink ref="ES74" r:id="rId125"/>
+    <hyperlink ref="ES75" r:id="rId126"/>
+    <hyperlink ref="ES76" r:id="rId127"/>
+    <hyperlink ref="ES77" r:id="rId128"/>
+    <hyperlink ref="ES78" r:id="rId129"/>
+    <hyperlink ref="ES79" r:id="rId130"/>
+    <hyperlink ref="ES80" r:id="rId131"/>
+    <hyperlink ref="ES81" r:id="rId132"/>
+    <hyperlink ref="ES82" r:id="rId133"/>
+    <hyperlink ref="ES83" r:id="rId134"/>
+    <hyperlink ref="ES84" r:id="rId135"/>
+    <hyperlink ref="ES85" r:id="rId136"/>
+    <hyperlink ref="ES86" r:id="rId137"/>
+    <hyperlink ref="ES87" r:id="rId138"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="100">
-    <tablePart r:id="rId137"/>
-    <tablePart r:id="rId138"/>
     <tablePart r:id="rId139"/>
     <tablePart r:id="rId140"/>
     <tablePart r:id="rId141"/>
@@ -52940,6 +52958,8 @@
     <tablePart r:id="rId234"/>
     <tablePart r:id="rId235"/>
     <tablePart r:id="rId236"/>
+    <tablePart r:id="rId237"/>
+    <tablePart r:id="rId238"/>
   </tableParts>
 </worksheet>
 </file>
@@ -53081,76 +53101,76 @@
         <v>10</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>2737</v>
+        <v>2739</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>2738</v>
+        <v>2740</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>2739</v>
+        <v>2741</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>2740</v>
+        <v>2742</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>2741</v>
+        <v>2743</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>2742</v>
+        <v>2744</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>2743</v>
+        <v>2745</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>2744</v>
+        <v>2746</v>
       </c>
       <c r="J1" s="7" t="s">
-        <v>2746</v>
+        <v>2748</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>2747</v>
+        <v>2749</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>2748</v>
+        <v>2750</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>2749</v>
+        <v>2751</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>2750</v>
+        <v>2752</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>2751</v>
+        <v>2753</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>2752</v>
+        <v>2754</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>2753</v>
+        <v>2755</v>
       </c>
       <c r="R1" s="7" t="s">
-        <v>2755</v>
+        <v>2757</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>2756</v>
+        <v>2758</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>2757</v>
+        <v>2759</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>2758</v>
+        <v>2760</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>2759</v>
+        <v>2761</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>2760</v>
+        <v>2762</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>2761</v>
+        <v>2763</v>
       </c>
       <c r="Y1" s="1" t="s">
-        <v>2762</v>
+        <v>2764</v>
       </c>
       <c r="Z1" s="1" t="s">
         <v>241</v>
@@ -53159,91 +53179,91 @@
         <v>242</v>
       </c>
       <c r="AB1" s="1" t="s">
-        <v>2763</v>
+        <v>2765</v>
       </c>
       <c r="AC1" s="1" t="s">
-        <v>2764</v>
+        <v>2766</v>
       </c>
       <c r="AD1" s="1" t="s">
-        <v>2765</v>
+        <v>2767</v>
       </c>
       <c r="AE1" s="1" t="s">
-        <v>2766</v>
+        <v>2768</v>
       </c>
       <c r="AF1" s="1" t="s">
-        <v>2767</v>
+        <v>2769</v>
       </c>
       <c r="AG1" s="1" t="s">
-        <v>2768</v>
+        <v>2770</v>
       </c>
       <c r="AH1" s="1" t="s">
-        <v>2769</v>
+        <v>2771</v>
       </c>
       <c r="AI1" s="1" t="s">
-        <v>2770</v>
+        <v>2772</v>
       </c>
       <c r="AJ1" s="1" t="s">
-        <v>2771</v>
+        <v>2773</v>
       </c>
       <c r="AK1" s="1" t="s">
-        <v>2772</v>
+        <v>2774</v>
       </c>
       <c r="AL1" s="1" t="s">
-        <v>2773</v>
+        <v>2775</v>
       </c>
       <c r="AM1" s="1" t="s">
-        <v>2774</v>
+        <v>2776</v>
       </c>
       <c r="AN1" s="1" t="s">
-        <v>2775</v>
+        <v>2777</v>
       </c>
       <c r="AO1" s="1" t="s">
-        <v>2776</v>
+        <v>2778</v>
       </c>
       <c r="AP1" s="1" t="s">
-        <v>2777</v>
+        <v>2779</v>
       </c>
       <c r="AQ1" s="1" t="s">
-        <v>2778</v>
+        <v>2780</v>
       </c>
       <c r="AR1" s="1" t="s">
-        <v>2779</v>
+        <v>2781</v>
       </c>
       <c r="AS1" s="1" t="s">
-        <v>2781</v>
+        <v>2783</v>
       </c>
       <c r="AT1" s="1" t="s">
-        <v>2782</v>
+        <v>2784</v>
       </c>
       <c r="AU1" s="1" t="s">
-        <v>2783</v>
+        <v>2785</v>
       </c>
       <c r="AV1" s="1" t="s">
-        <v>2784</v>
+        <v>2786</v>
       </c>
       <c r="AW1" s="1" t="s">
-        <v>2785</v>
+        <v>2787</v>
       </c>
       <c r="AX1" s="1" t="s">
-        <v>2786</v>
+        <v>2788</v>
       </c>
       <c r="AY1" s="1" t="s">
-        <v>2787</v>
+        <v>2789</v>
       </c>
       <c r="AZ1" s="1" t="s">
-        <v>2788</v>
+        <v>2790</v>
       </c>
       <c r="BA1" s="1" t="s">
-        <v>2789</v>
+        <v>2791</v>
       </c>
       <c r="BB1" s="1" t="s">
-        <v>2790</v>
+        <v>2792</v>
       </c>
       <c r="BC1" s="1" t="s">
-        <v>2791</v>
+        <v>2793</v>
       </c>
       <c r="BD1" s="1" t="s">
-        <v>2792</v>
+        <v>2794</v>
       </c>
       <c r="BE1" s="1" t="s">
         <v>2457</v>
@@ -53309,100 +53329,100 @@
         <v>2477</v>
       </c>
       <c r="BZ1" s="1" t="s">
-        <v>2795</v>
+        <v>2797</v>
       </c>
       <c r="CA1" s="1" t="s">
-        <v>2796</v>
+        <v>2798</v>
       </c>
       <c r="CB1" s="1" t="s">
-        <v>2797</v>
+        <v>2799</v>
       </c>
       <c r="CC1" s="1" t="s">
-        <v>2798</v>
+        <v>2800</v>
       </c>
       <c r="CD1" s="1" t="s">
-        <v>2799</v>
+        <v>2801</v>
       </c>
       <c r="CE1" s="1" t="s">
-        <v>2800</v>
+        <v>2802</v>
       </c>
       <c r="CF1" s="1" t="s">
-        <v>2801</v>
+        <v>2803</v>
       </c>
       <c r="CG1" s="1" t="s">
-        <v>2802</v>
+        <v>2804</v>
       </c>
       <c r="CH1" s="1" t="s">
-        <v>2803</v>
+        <v>2805</v>
       </c>
       <c r="CI1" s="1" t="s">
-        <v>2804</v>
+        <v>2806</v>
       </c>
       <c r="CJ1" s="1" t="s">
-        <v>2805</v>
+        <v>2807</v>
       </c>
       <c r="CK1" s="1" t="s">
-        <v>2806</v>
+        <v>2808</v>
       </c>
       <c r="CL1" s="1" t="s">
-        <v>2807</v>
+        <v>2809</v>
       </c>
       <c r="CM1" s="1" t="s">
-        <v>2808</v>
+        <v>2810</v>
       </c>
       <c r="CN1" s="1" t="s">
-        <v>2809</v>
+        <v>2811</v>
       </c>
       <c r="CO1" s="1" t="s">
-        <v>2810</v>
+        <v>2812</v>
       </c>
       <c r="CP1" s="1" t="s">
-        <v>2811</v>
+        <v>2813</v>
       </c>
       <c r="CQ1" s="1" t="s">
-        <v>2812</v>
+        <v>2814</v>
       </c>
       <c r="CR1" s="1" t="s">
-        <v>2813</v>
+        <v>2815</v>
       </c>
       <c r="CS1" s="1" t="s">
-        <v>2814</v>
+        <v>2816</v>
       </c>
       <c r="CT1" s="1" t="s">
-        <v>2815</v>
+        <v>2817</v>
       </c>
       <c r="CU1" s="1" t="s">
-        <v>2816</v>
+        <v>2818</v>
       </c>
       <c r="CV1" s="1" t="s">
-        <v>2817</v>
+        <v>2819</v>
       </c>
       <c r="CW1" s="1" t="s">
-        <v>2818</v>
+        <v>2820</v>
       </c>
       <c r="CX1" s="1" t="s">
-        <v>2819</v>
+        <v>2821</v>
       </c>
       <c r="CY1" s="1" t="s">
-        <v>2820</v>
+        <v>2822</v>
       </c>
       <c r="CZ1" s="1" t="s">
-        <v>2821</v>
+        <v>2823</v>
       </c>
       <c r="DA1" s="1" t="s">
-        <v>2822</v>
+        <v>2824</v>
       </c>
       <c r="DB1" s="1" t="s">
         <v>249</v>
       </c>
       <c r="DC1" s="1" t="s">
-        <v>2823</v>
+        <v>2825</v>
       </c>
       <c r="DD1" s="1" t="s">
-        <v>2825</v>
+        <v>2827</v>
       </c>
       <c r="DE1" s="1" t="s">
-        <v>2827</v>
+        <v>2829</v>
       </c>
       <c r="DF1" s="1" t="s">
         <v>287</v>
@@ -53461,7 +53481,7 @@
         <v>10</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>2745</v>
+        <v>2747</v>
       </c>
       <c r="C2" s="8"/>
       <c r="D2" s="8"/>
@@ -53471,7 +53491,7 @@
       <c r="H2" s="8"/>
       <c r="I2" s="8"/>
       <c r="J2" s="8" t="s">
-        <v>2754</v>
+        <v>2756</v>
       </c>
       <c r="K2" s="8"/>
       <c r="L2" s="8"/>
@@ -53495,13 +53515,13 @@
       </c>
       <c r="AA2" s="1"/>
       <c r="AB2" s="1" t="s">
-        <v>2763</v>
+        <v>2765</v>
       </c>
       <c r="AC2" s="1" t="s">
-        <v>2764</v>
+        <v>2766</v>
       </c>
       <c r="AD2" s="1" t="s">
-        <v>2765</v>
+        <v>2767</v>
       </c>
       <c r="AE2" s="1" t="s">
         <v>25</v>
@@ -53584,7 +53604,7 @@
         <v>249</v>
       </c>
       <c r="DC2" s="1" t="s">
-        <v>2829</v>
+        <v>2831</v>
       </c>
       <c r="DD2" s="1"/>
       <c r="DE2" s="1"/>
@@ -53741,13 +53761,13 @@
       </c>
       <c r="DA3" s="1"/>
       <c r="DC3" s="1" t="s">
-        <v>2824</v>
+        <v>2826</v>
       </c>
       <c r="DD3" s="1" t="s">
-        <v>2826</v>
+        <v>2828</v>
       </c>
       <c r="DE3" s="1" t="s">
-        <v>2828</v>
+        <v>2830</v>
       </c>
       <c r="DG3" s="8" t="s">
         <v>35</v>
@@ -53851,7 +53871,7 @@
         <v>18</v>
       </c>
       <c r="AE4" s="8" t="s">
-        <v>2794</v>
+        <v>2796</v>
       </c>
       <c r="AF4" s="8"/>
       <c r="AG4" s="8"/>
@@ -53973,7 +53993,7 @@
         <v>109</v>
       </c>
       <c r="AG5" s="1" t="s">
-        <v>2780</v>
+        <v>2782</v>
       </c>
       <c r="AH5" s="1"/>
       <c r="AI5" s="1"/>
@@ -53987,7 +54007,7 @@
       <c r="AQ5" s="1"/>
       <c r="AR5" s="1"/>
       <c r="AS5" s="1" t="s">
-        <v>2793</v>
+        <v>2795</v>
       </c>
       <c r="AT5" s="1"/>
       <c r="AU5" s="1"/>
@@ -54036,7 +54056,7 @@
         <v>135</v>
       </c>
       <c r="BZ5" s="1" t="s">
-        <v>2794</v>
+        <v>2796</v>
       </c>
       <c r="CA5" s="1"/>
       <c r="CB5" s="1"/>
@@ -54128,7 +54148,7 @@
         <v>109</v>
       </c>
       <c r="CB6" s="1" t="s">
-        <v>2780</v>
+        <v>2782</v>
       </c>
       <c r="CC6" s="1"/>
       <c r="CD6" s="1"/>
@@ -54142,7 +54162,7 @@
       <c r="CL6" s="1"/>
       <c r="CM6" s="1"/>
       <c r="CN6" s="1" t="s">
-        <v>2793</v>
+        <v>2795</v>
       </c>
       <c r="CO6" s="1"/>
       <c r="CP6" s="1"/>
@@ -54687,76 +54707,76 @@
         <v>10</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>2737</v>
+        <v>2739</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>2738</v>
+        <v>2740</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>2739</v>
+        <v>2741</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>2740</v>
+        <v>2742</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>2741</v>
+        <v>2743</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>2742</v>
+        <v>2744</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>2743</v>
+        <v>2745</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>2744</v>
+        <v>2746</v>
       </c>
       <c r="J15" s="7" t="s">
-        <v>2746</v>
+        <v>2748</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>2747</v>
+        <v>2749</v>
       </c>
       <c r="L15" s="1" t="s">
-        <v>2748</v>
+        <v>2750</v>
       </c>
       <c r="M15" s="1" t="s">
-        <v>2749</v>
+        <v>2751</v>
       </c>
       <c r="N15" s="1" t="s">
-        <v>2750</v>
+        <v>2752</v>
       </c>
       <c r="O15" s="1" t="s">
-        <v>2751</v>
+        <v>2753</v>
       </c>
       <c r="P15" s="1" t="s">
-        <v>2752</v>
+        <v>2754</v>
       </c>
       <c r="Q15" s="1" t="s">
-        <v>2753</v>
+        <v>2755</v>
       </c>
       <c r="R15" s="7" t="s">
-        <v>2755</v>
+        <v>2757</v>
       </c>
       <c r="S15" s="1" t="s">
-        <v>2756</v>
+        <v>2758</v>
       </c>
       <c r="T15" s="1" t="s">
-        <v>2757</v>
+        <v>2759</v>
       </c>
       <c r="U15" s="1" t="s">
-        <v>2758</v>
+        <v>2760</v>
       </c>
       <c r="V15" s="1" t="s">
-        <v>2759</v>
+        <v>2761</v>
       </c>
       <c r="W15" s="1" t="s">
-        <v>2760</v>
+        <v>2762</v>
       </c>
       <c r="X15" s="1" t="s">
-        <v>2761</v>
+        <v>2763</v>
       </c>
       <c r="Y15" s="1" t="s">
-        <v>2762</v>
+        <v>2764</v>
       </c>
       <c r="Z15" s="1" t="s">
         <v>241</v>
@@ -54765,91 +54785,91 @@
         <v>242</v>
       </c>
       <c r="AB15" s="1" t="s">
-        <v>2763</v>
+        <v>2765</v>
       </c>
       <c r="AC15" s="1" t="s">
-        <v>2764</v>
+        <v>2766</v>
       </c>
       <c r="AD15" s="1" t="s">
-        <v>2765</v>
+        <v>2767</v>
       </c>
       <c r="AE15" s="1" t="s">
-        <v>2766</v>
+        <v>2768</v>
       </c>
       <c r="AF15" s="1" t="s">
-        <v>2767</v>
+        <v>2769</v>
       </c>
       <c r="AG15" s="1" t="s">
-        <v>2768</v>
+        <v>2770</v>
       </c>
       <c r="AH15" s="1" t="s">
-        <v>2769</v>
+        <v>2771</v>
       </c>
       <c r="AI15" s="1" t="s">
-        <v>2770</v>
+        <v>2772</v>
       </c>
       <c r="AJ15" s="1" t="s">
-        <v>2771</v>
+        <v>2773</v>
       </c>
       <c r="AK15" s="1" t="s">
-        <v>2772</v>
+        <v>2774</v>
       </c>
       <c r="AL15" s="1" t="s">
-        <v>2773</v>
+        <v>2775</v>
       </c>
       <c r="AM15" s="1" t="s">
-        <v>2774</v>
+        <v>2776</v>
       </c>
       <c r="AN15" s="1" t="s">
-        <v>2775</v>
+        <v>2777</v>
       </c>
       <c r="AO15" s="1" t="s">
-        <v>2776</v>
+        <v>2778</v>
       </c>
       <c r="AP15" s="1" t="s">
-        <v>2777</v>
+        <v>2779</v>
       </c>
       <c r="AQ15" s="1" t="s">
-        <v>2778</v>
+        <v>2780</v>
       </c>
       <c r="AR15" s="1" t="s">
-        <v>2779</v>
+        <v>2781</v>
       </c>
       <c r="AS15" s="1" t="s">
-        <v>2781</v>
+        <v>2783</v>
       </c>
       <c r="AT15" s="1" t="s">
-        <v>2782</v>
+        <v>2784</v>
       </c>
       <c r="AU15" s="1" t="s">
-        <v>2783</v>
+        <v>2785</v>
       </c>
       <c r="AV15" s="1" t="s">
-        <v>2784</v>
+        <v>2786</v>
       </c>
       <c r="AW15" s="1" t="s">
-        <v>2785</v>
+        <v>2787</v>
       </c>
       <c r="AX15" s="1" t="s">
-        <v>2786</v>
+        <v>2788</v>
       </c>
       <c r="AY15" s="1" t="s">
-        <v>2787</v>
+        <v>2789</v>
       </c>
       <c r="AZ15" s="1" t="s">
-        <v>2788</v>
+        <v>2790</v>
       </c>
       <c r="BA15" s="1" t="s">
-        <v>2789</v>
+        <v>2791</v>
       </c>
       <c r="BB15" s="1" t="s">
-        <v>2790</v>
+        <v>2792</v>
       </c>
       <c r="BC15" s="1" t="s">
-        <v>2791</v>
+        <v>2793</v>
       </c>
       <c r="BD15" s="1" t="s">
-        <v>2792</v>
+        <v>2794</v>
       </c>
       <c r="BE15" s="1" t="s">
         <v>2457</v>
@@ -54915,100 +54935,100 @@
         <v>2477</v>
       </c>
       <c r="BZ15" s="1" t="s">
-        <v>2795</v>
+        <v>2797</v>
       </c>
       <c r="CA15" s="1" t="s">
-        <v>2796</v>
+        <v>2798</v>
       </c>
       <c r="CB15" s="1" t="s">
-        <v>2797</v>
+        <v>2799</v>
       </c>
       <c r="CC15" s="1" t="s">
-        <v>2798</v>
+        <v>2800</v>
       </c>
       <c r="CD15" s="1" t="s">
-        <v>2799</v>
+        <v>2801</v>
       </c>
       <c r="CE15" s="1" t="s">
-        <v>2800</v>
+        <v>2802</v>
       </c>
       <c r="CF15" s="1" t="s">
-        <v>2801</v>
+        <v>2803</v>
       </c>
       <c r="CG15" s="1" t="s">
-        <v>2802</v>
+        <v>2804</v>
       </c>
       <c r="CH15" s="1" t="s">
-        <v>2803</v>
+        <v>2805</v>
       </c>
       <c r="CI15" s="1" t="s">
-        <v>2804</v>
+        <v>2806</v>
       </c>
       <c r="CJ15" s="1" t="s">
-        <v>2805</v>
+        <v>2807</v>
       </c>
       <c r="CK15" s="1" t="s">
-        <v>2806</v>
+        <v>2808</v>
       </c>
       <c r="CL15" s="1" t="s">
-        <v>2807</v>
+        <v>2809</v>
       </c>
       <c r="CM15" s="1" t="s">
-        <v>2808</v>
+        <v>2810</v>
       </c>
       <c r="CN15" s="1" t="s">
-        <v>2809</v>
+        <v>2811</v>
       </c>
       <c r="CO15" s="1" t="s">
-        <v>2810</v>
+        <v>2812</v>
       </c>
       <c r="CP15" s="1" t="s">
-        <v>2811</v>
+        <v>2813</v>
       </c>
       <c r="CQ15" s="1" t="s">
-        <v>2812</v>
+        <v>2814</v>
       </c>
       <c r="CR15" s="1" t="s">
-        <v>2813</v>
+        <v>2815</v>
       </c>
       <c r="CS15" s="1" t="s">
-        <v>2814</v>
+        <v>2816</v>
       </c>
       <c r="CT15" s="1" t="s">
-        <v>2815</v>
+        <v>2817</v>
       </c>
       <c r="CU15" s="1" t="s">
-        <v>2816</v>
+        <v>2818</v>
       </c>
       <c r="CV15" s="1" t="s">
-        <v>2817</v>
+        <v>2819</v>
       </c>
       <c r="CW15" s="1" t="s">
-        <v>2818</v>
+        <v>2820</v>
       </c>
       <c r="CX15" s="1" t="s">
-        <v>2819</v>
+        <v>2821</v>
       </c>
       <c r="CY15" s="1" t="s">
-        <v>2820</v>
+        <v>2822</v>
       </c>
       <c r="CZ15" s="1" t="s">
-        <v>2821</v>
+        <v>2823</v>
       </c>
       <c r="DA15" s="1" t="s">
-        <v>2822</v>
+        <v>2824</v>
       </c>
       <c r="DB15" s="1" t="s">
         <v>249</v>
       </c>
       <c r="DC15" s="1" t="s">
-        <v>2823</v>
+        <v>2825</v>
       </c>
       <c r="DD15" s="1" t="s">
-        <v>2825</v>
+        <v>2827</v>
       </c>
       <c r="DE15" s="1" t="s">
-        <v>2827</v>
+        <v>2829</v>
       </c>
       <c r="DF15" s="1" t="s">
         <v>287</v>
@@ -55214,50 +55234,50 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
-        <v>2870</v>
+        <v>2872</v>
       </c>
       <c r="B1" t="s">
-        <v>2871</v>
+        <v>2873</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>2872</v>
+        <v>2874</v>
       </c>
       <c r="B2" t="s">
-        <v>2873</v>
+        <v>2875</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>2874</v>
+        <v>2876</v>
       </c>
       <c r="B3" t="s">
-        <v>2875</v>
+        <v>2877</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>2876</v>
+        <v>2878</v>
       </c>
       <c r="B4" t="s">
-        <v>2877</v>
+        <v>2879</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>2878</v>
+        <v>2880</v>
       </c>
       <c r="B5" t="s">
-        <v>2879</v>
+        <v>2881</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>2880</v>
+        <v>2882</v>
       </c>
       <c r="B6" t="s">
-        <v>2881</v>
+        <v>2883</v>
       </c>
     </row>
   </sheetData>
@@ -64571,7 +64591,7 @@
       <formula1>'Codelijsten'!$ES$4:$ES$87</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I7:I1000001">
-      <formula1>'Codelijsten'!$EU$4:$EU$12</formula1>
+      <formula1>'Codelijsten'!$EU$4:$EU$14</formula1>
     </dataValidation>
     <dataValidation type="date" operator="greaterThan" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="T7:T1000001">
       <formula1>-146096</formula1>
@@ -64697,61 +64717,61 @@
   <sheetData>
     <row r="1" spans="1:78" hidden="1">
       <c r="A1" s="9" t="s">
-        <v>2710</v>
+        <v>2712</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>2711</v>
+        <v>2713</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>2713</v>
+        <v>2715</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>2714</v>
+        <v>2716</v>
       </c>
       <c r="E1" s="9" t="s">
-        <v>2715</v>
+        <v>2717</v>
       </c>
       <c r="F1" s="9" t="s">
-        <v>2716</v>
+        <v>2718</v>
       </c>
       <c r="G1" s="11" t="s">
-        <v>2717</v>
+        <v>2719</v>
       </c>
       <c r="H1" s="11" t="s">
-        <v>2718</v>
+        <v>2720</v>
       </c>
       <c r="I1" s="11" t="s">
-        <v>2719</v>
+        <v>2721</v>
       </c>
       <c r="J1" s="11" t="s">
-        <v>2720</v>
+        <v>2722</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>2721</v>
+        <v>2723</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>2722</v>
+        <v>2724</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>2723</v>
+        <v>2725</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>2724</v>
+        <v>2726</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>2725</v>
+        <v>2727</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>2726</v>
+        <v>2728</v>
       </c>
       <c r="Q1" s="9" t="s">
-        <v>2728</v>
+        <v>2730</v>
       </c>
       <c r="R1" s="9" t="s">
-        <v>2729</v>
+        <v>2731</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>2730</v>
+        <v>2732</v>
       </c>
       <c r="T1" s="1" t="s">
         <v>2496</v>
@@ -65060,7 +65080,7 @@
         <v>1108</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>2712</v>
+        <v>2714</v>
       </c>
       <c r="C3" s="8" t="s">
         <v>1110</v>
@@ -65069,7 +65089,7 @@
         <v>1112</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>2727</v>
+        <v>2729</v>
       </c>
       <c r="F3" s="8"/>
       <c r="G3" s="8"/>
@@ -65083,7 +65103,7 @@
       <c r="O3" s="8"/>
       <c r="P3" s="8"/>
       <c r="Q3" s="8" t="s">
-        <v>2732</v>
+        <v>2734</v>
       </c>
       <c r="R3" s="8"/>
       <c r="S3" s="8"/>
@@ -65218,7 +65238,7 @@
         <v>1204</v>
       </c>
       <c r="Q4" s="8" t="s">
-        <v>2731</v>
+        <v>2733</v>
       </c>
       <c r="R4" s="8"/>
       <c r="S4" s="8"/>
@@ -65365,61 +65385,61 @@
     </row>
     <row r="7" spans="1:78">
       <c r="A7" s="9" t="s">
-        <v>2710</v>
+        <v>2712</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>2711</v>
+        <v>2713</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>2713</v>
+        <v>2715</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>2714</v>
+        <v>2716</v>
       </c>
       <c r="E7" s="9" t="s">
-        <v>2715</v>
+        <v>2717</v>
       </c>
       <c r="F7" s="9" t="s">
-        <v>2716</v>
+        <v>2718</v>
       </c>
       <c r="G7" s="11" t="s">
-        <v>2717</v>
+        <v>2719</v>
       </c>
       <c r="H7" s="11" t="s">
-        <v>2718</v>
+        <v>2720</v>
       </c>
       <c r="I7" s="11" t="s">
-        <v>2719</v>
+        <v>2721</v>
       </c>
       <c r="J7" s="11" t="s">
-        <v>2720</v>
+        <v>2722</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>2721</v>
+        <v>2723</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>2722</v>
+        <v>2724</v>
       </c>
       <c r="M7" s="1" t="s">
-        <v>2723</v>
+        <v>2725</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>2724</v>
+        <v>2726</v>
       </c>
       <c r="O7" s="1" t="s">
-        <v>2725</v>
+        <v>2727</v>
       </c>
       <c r="P7" s="1" t="s">
-        <v>2726</v>
+        <v>2728</v>
       </c>
       <c r="Q7" s="9" t="s">
-        <v>2728</v>
+        <v>2730</v>
       </c>
       <c r="R7" s="9" t="s">
-        <v>2729</v>
+        <v>2731</v>
       </c>
       <c r="S7" s="1" t="s">
-        <v>2730</v>
+        <v>2732</v>
       </c>
       <c r="T7" s="1" t="s">
         <v>2496</v>

--- a/templates/oefen/oefen_bodem_template_full.xlsx
+++ b/templates/oefen/oefen_bodem_template_full.xlsx
@@ -8645,19 +8645,19 @@
     <t>Date generated</t>
   </si>
   <si>
-    <t>2026-05-06 16:21:32.226048</t>
+    <t>2026-05-19 11:29:05.722980</t>
   </si>
   <si>
     <t>version</t>
   </si>
   <si>
-    <t>2.3.1</t>
+    <t>2.4.0</t>
   </si>
   <si>
     <t>xdov-version</t>
   </si>
   <si>
-    <t>10.1.0</t>
+    <t>10.2.0</t>
   </si>
   <si>
     <t>schema-version</t>

--- a/templates/oefen/oefen_bodem_template_full.xlsx
+++ b/templates/oefen/oefen_bodem_template_full.xlsx
@@ -8645,13 +8645,13 @@
     <t>Date generated</t>
   </si>
   <si>
-    <t>2026-05-19 11:29:05.722980</t>
+    <t>2026-05-19 14:52:56.786419</t>
   </si>
   <si>
     <t>version</t>
   </si>
   <si>
-    <t>2.4.0</t>
+    <t>2.4.1</t>
   </si>
   <si>
     <t>xdov-version</t>
